--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487467_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487467_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.305199999999999</v>
+        <v>8.068099999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3246</v>
+        <v>9.0341</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0195</v>
+        <v>-0.966</v>
       </c>
       <c r="G2" t="n">
         <v>4.1541</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7179</v>
+        <v>0.4808</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0081</v>
+        <v>0.7175</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2902</v>
+        <v>-0.2367</v>
       </c>
       <c r="V2" t="n">
         <v>3.0415</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>J. CONNELL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7742</v>
+        <v>5.3801</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9736</v>
+        <v>6.1243</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1994</v>
+        <v>-0.7442</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9527</v>
+        <v>5.6916</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9728</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.98</v>
+        <v>4.7386</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5058</v>
+        <v>5.6885</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1268</v>
+        <v>1.3593</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3789</v>
+        <v>4.3292</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.553</v>
+        <v>0.0031</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1541</v>
+        <v>-0.4062</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.399</v>
+        <v>0.4093</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4331</v>
+        <v>0.73</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4158</v>
+        <v>0.4358</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0173</v>
+        <v>0.2942</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8837</v>
+        <v>-1.8249</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CONNELL</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5196</v>
+        <v>5.1512</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4509</v>
+        <v>5.2971</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9313</v>
+        <v>-0.1459</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6916</v>
+        <v>2.9527</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9530999999999999</v>
+        <v>1.9728</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7386</v>
+        <v>0.98</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6885</v>
+        <v>4.5058</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3593</v>
+        <v>3.1268</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3292</v>
+        <v>1.3789</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0031</v>
+        <v>-1.553</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4062</v>
+        <v>-1.1541</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4093</v>
+        <v>-0.399</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1305</v>
+        <v>-0.0562</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2376</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1071</v>
+        <v>0.0362</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8249</v>
+        <v>0.8837</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6983</v>
+        <v>3.3276</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1555</v>
+        <v>1.865</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5428</v>
+        <v>1.4626</v>
       </c>
       <c r="G5" t="n">
         <v>1.4987</v>
@@ -844,13 +844,13 @@
         <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2998</v>
+        <v>0.9291</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8299</v>
+        <v>0.5393</v>
       </c>
       <c r="U5" t="n">
-        <v>0.47</v>
+        <v>0.3898</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2754</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8141</v>
+        <v>2.4542</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4604</v>
+        <v>7.5453</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6463</v>
+        <v>-5.0911</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5942</v>
+        <v>3.6379</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2865</v>
+        <v>1.602</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6922</v>
+        <v>2.036</v>
       </c>
       <c r="J6" t="n">
-        <v>3.491</v>
+        <v>7.0148</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1677</v>
+        <v>3.7768</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3233</v>
+        <v>3.238</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8968</v>
+        <v>-3.3769</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8812</v>
+        <v>-2.1748</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0156</v>
+        <v>-1.2021</v>
       </c>
       <c r="P6" t="n">
         <v>1.3709</v>
@@ -922,28 +922,28 @@
         <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8489</v>
+        <v>0.4868</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0306</v>
+        <v>0.5305</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8794999999999999</v>
+        <v>-0.0437</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-3.0415</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2109</v>
+        <v>2.3481</v>
       </c>
       <c r="E7" t="n">
-        <v>7.2218</v>
+        <v>3.3151</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.0109</v>
+        <v>-0.9671</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6379</v>
+        <v>0.5942</v>
       </c>
       <c r="H7" t="n">
-        <v>1.602</v>
+        <v>2.2865</v>
       </c>
       <c r="I7" t="n">
-        <v>2.036</v>
+        <v>-1.6922</v>
       </c>
       <c r="J7" t="n">
-        <v>7.0148</v>
+        <v>3.491</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7768</v>
+        <v>3.1677</v>
       </c>
       <c r="L7" t="n">
-        <v>3.238</v>
+        <v>0.3233</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.3769</v>
+        <v>-2.8968</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1748</v>
+        <v>-0.8812</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2021</v>
+        <v>-2.0156</v>
       </c>
       <c r="P7" t="n">
         <v>1.3709</v>
@@ -1000,22 +1000,22 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2435</v>
+        <v>0.3829</v>
       </c>
       <c r="T7" t="n">
-        <v>0.207</v>
+        <v>-0.1759</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0365</v>
+        <v>0.5587</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.0415</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.0415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.46</v>
+        <v>1.6928</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7725</v>
+        <v>4.1389</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3125</v>
+        <v>-2.4461</v>
       </c>
       <c r="G8" t="n">
         <v>0.801</v>
@@ -1078,13 +1078,13 @@
         <v>1.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5161</v>
+        <v>-0.2833</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5346</v>
+        <v>-0.1682</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0185</v>
+        <v>-0.1151</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2038</v>
+        <v>0.4665</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6977</v>
+        <v>1.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4939</v>
+        <v>-1.3335</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0154</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2193</v>
+        <v>0.482</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2664</v>
+        <v>0.3688</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0472</v>
+        <v>0.1132</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6551</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1592</v>
+        <v>-0.3045</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4959</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5244</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6943</v>
+        <v>0.4154</v>
       </c>
       <c r="T10" t="n">
-        <v>0.207</v>
+        <v>0.0618</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4873</v>
+        <v>0.3536</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9572</v>
+        <v>-1.4199</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4086</v>
+        <v>0.732</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3657</v>
+        <v>-2.1519</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1357</v>
@@ -1312,13 +1312,13 @@
         <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3295</v>
+        <v>-0.7922</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7128</v>
+        <v>-0.3893</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6167</v>
+        <v>-0.4029</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6835</v>
+        <v>-2.63</v>
       </c>
       <c r="E12" t="n">
         <v>-0.7588</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9247</v>
+        <v>-1.8712</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3243</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1426</v>
+        <v>-0.0891</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2166</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2771</v>
+        <v>-3.6003</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9774</v>
+        <v>-1.3273</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2997</v>
+        <v>-2.273</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4874</v>
@@ -1468,13 +1468,13 @@
         <v>0.1958</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1896</v>
+        <v>-0.1337</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3852</v>
+        <v>0.0353</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1957</v>
+        <v>-0.1689</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.4132</v>
+        <v>20.3044</v>
       </c>
       <c r="E14" t="n">
-        <v>36.5702</v>
+        <v>37.4612</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.157</v>
+        <v>-17.1569</v>
       </c>
       <c r="G14" t="n">
         <v>13.843</v>
@@ -1516,7 +1516,7 @@
         <v>8.515100000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>5.328200000000001</v>
+        <v>5.328199999999999</v>
       </c>
       <c r="J14" t="n">
         <v>37.4513</v>
@@ -1546,13 +1546,13 @@
         <v>13.7091</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6615</v>
+        <v>2.552499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7940000000000003</v>
+        <v>1.6851</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8674999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-3.925199999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3807</v>
+        <v>0.496</v>
       </c>
       <c r="E15" t="n">
-        <v>5.627</v>
+        <v>6.0363</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.2463</v>
+        <v>-5.5403</v>
       </c>
       <c r="G15" t="n">
         <v>3.1896</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1669</v>
+        <v>0.2822</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8316</v>
+        <v>-0.4223</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.7044</v>
       </c>
       <c r="V15" t="n">
         <v>0.9412</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1263</v>
+        <v>-0.3852</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1339</v>
+        <v>2.6474</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.0076</v>
+        <v>-3.0326</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5708</v>
+        <v>0.237</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9705</v>
+        <v>0.7672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3997</v>
+        <v>-0.5302</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7561</v>
+        <v>3.2733</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0887</v>
+        <v>3.1473</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6674</v>
+        <v>0.1261</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.3268</v>
+        <v>-3.0363</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.0591</v>
+        <v>-2.38</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2677</v>
+        <v>-0.6563</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1958</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6763</v>
+        <v>-0.7433</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8651</v>
+        <v>-0.1594</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1888</v>
+        <v>-0.5839</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2166</v>
+        <v>1.492</v>
       </c>
       <c r="W16" t="n">
         <v>1.492</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6747</v>
+        <v>-0.4075</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5451</v>
+        <v>4.5199</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2197</v>
+        <v>-4.9275</v>
       </c>
       <c r="G17" t="n">
-        <v>0.237</v>
+        <v>-1.5708</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7672</v>
+        <v>-1.9705</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5302</v>
+        <v>0.3997</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2733</v>
+        <v>3.7561</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1473</v>
+        <v>1.0887</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1261</v>
+        <v>2.6674</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.0363</v>
+        <v>-5.3268</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.38</v>
+        <v>-3.0591</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6563</v>
+        <v>-2.2677</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0327</v>
+        <v>0.1425</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2617</v>
+        <v>0.2511</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.771</v>
+        <v>-0.1087</v>
       </c>
       <c r="V17" t="n">
-        <v>1.492</v>
+        <v>1.2166</v>
       </c>
       <c r="W17" t="n">
         <v>1.492</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8061</v>
+        <v>-0.7572</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2021</v>
+        <v>1.3044</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0082</v>
+        <v>-2.0616</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6163</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7773</v>
+        <v>-0.7284</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1429</v>
+        <v>-0.0406</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6344</v>
+        <v>-0.6878</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5112</v>
+        <v>-1.053</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5966</v>
+        <v>4.1083</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.1078</v>
+        <v>-5.1612</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1488</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6585</v>
+        <v>-0.2003</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4399</v>
+        <v>0.0717</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2185</v>
+        <v>-0.272</v>
       </c>
       <c r="V19" t="n">
         <v>1.492</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8686</v>
+        <v>-1.7663</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1978</v>
+        <v>0.3001</v>
       </c>
       <c r="F20" t="n">
         <v>-2.0664</v>
@@ -2014,10 +2014,10 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.724</v>
+        <v>-0.6217</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0353</v>
+        <v>0.1376</v>
       </c>
       <c r="U20" t="n">
         <v>-0.7593</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5767</v>
+        <v>-4.8048</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0396</v>
+        <v>0.9216</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.6163</v>
+        <v>-5.7263</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5231</v>
+        <v>-6.0524</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3964</v>
+        <v>-2.4506</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9195</v>
+        <v>-3.6018</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3257</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>2.164</v>
+        <v>-0.0716</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1617</v>
+        <v>-0.5206</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.8488</v>
+        <v>-5.4602</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7676</v>
+        <v>-2.379</v>
       </c>
       <c r="O21" t="n">
         <v>-3.0812</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3173</v>
+        <v>0.0518</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6516</v>
+        <v>-0.3111</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6657</v>
+        <v>0.3629</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2166</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9163</v>
+        <v>-5.3354</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0239</v>
+        <v>-2.0043</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.9402</v>
+        <v>-3.3311</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.0524</v>
+        <v>-2.8219</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4506</v>
+        <v>-1.5086</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.6018</v>
+        <v>-1.3133</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.2842</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0716</v>
+        <v>0.1225</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5206</v>
+        <v>0.1617</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.4602</v>
+        <v>-3.1061</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.379</v>
+        <v>-1.6311</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.0812</v>
+        <v>-1.475</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5875</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0598</v>
+        <v>-0.3383</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2088</v>
+        <v>-0.3299</v>
       </c>
       <c r="U22" t="n">
-        <v>0.149</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6083</v>
+        <v>-0.6083</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5668</v>
+        <v>-5.4</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.209</v>
+        <v>-0.6768</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3578</v>
+        <v>-4.7232</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8219</v>
+        <v>-2.5231</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5086</v>
+        <v>0.3964</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3133</v>
+        <v>-2.9195</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2842</v>
+        <v>2.3257</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1225</v>
+        <v>2.164</v>
       </c>
       <c r="L23" t="n">
         <v>0.1617</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.1061</v>
+        <v>-4.8488</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6311</v>
+        <v>-1.7676</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.475</v>
+        <v>-3.0812</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5668</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5697</v>
+        <v>0.494</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5346</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0351</v>
+        <v>0.5587</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="24">
@@ -2284,10 +2284,10 @@
         <v>-19.4134</v>
       </c>
       <c r="E24" t="n">
-        <v>17.157</v>
+        <v>17.1569</v>
       </c>
       <c r="F24" t="n">
-        <v>-36.5703</v>
+        <v>-36.5702</v>
       </c>
       <c r="G24" t="n">
         <v>-13.843</v>
@@ -2317,7 +2317,7 @@
         <v>-16.0364</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.833900000000001</v>
+        <v>-7.8339</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.7093</v>
@@ -2329,10 +2329,10 @@
         <v>-1.6615</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8674999999999999</v>
+        <v>-0.8675999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7938999999999999</v>
+        <v>-0.7940999999999998</v>
       </c>
       <c r="V24" t="n">
         <v>3.9252</v>
